--- a/repertorio/ITALIA_NERA_RACCORDO_FASE_SETTIMA_MORO.xlsx
+++ b/repertorio/ITALIA_NERA_RACCORDO_FASE_SETTIMA_MORO.xlsx
@@ -610,7 +610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -765,91 +765,91 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Ottava</t>
+          <t>Settima</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Canale orientale; quarta persona nella base; Stato Zero di quattro apparati (XIII leg., doc. XXIII n.37, sem. gen. 2000)</t>
+          <t>L'organismo successore dichiara il proprio standard (XII leg., doc. XXIII n.1 e n.3, 1995): puo' andare 'oltre la prova processuale'. UNDICESIMA REGOLA: la sede conferisce pubblicita', non grado</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>LODO MORO e canale OLP (voce 40); Hyperion/Superclan (voci 40,42)</t>
+          <t>Gradazione del corpus: atti delle Commissioni = A per le acquisizioni, B per le ricostruzioni/valutazioni</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Il 'canale orientale' della relazione parlamentare e' il quadro del lodo Moro/OLP gia' censito; la 'quarta persona' e i rifiuti a comparire = fonti dichiarative negative</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr"/>
+          <t>FONDA la gradazione del corpus sulla dichiarazione della fonte medesima (non piu' solo prudenza dell'autore): es. Mastelloni/Hyperion doc. parlamentari registrati ma proscioglimento a C (voce 40)</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Nona</t>
+          <t>Ottava</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Fondo di 100 record di un servizio informativo estero (sala di lettura elettronica, marzo 2026)</t>
+          <t>Canale orientale; quarta persona nella base; Stato Zero di quattro apparati (XIII leg., doc. XXIII n.37, sem. gen. 2000)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Archivi del corpus: cia.gov/readingroom (ARCHIVI_OPERATIVO)</t>
+          <t>LODO MORO e canale OLP (voce 40); Hyperion/Superclan (voci 40,42)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Distinzione indirizzo/atto: i 100 record sono 'indirizzi', non 'atti posseduti' - stessa cautela del corpus sugli URL non controllati</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr"/>
+          <t>Il 'canale orientale' della relazione parlamentare e' il quadro del lodo Moro/OLP gia' censito; la 'quarta persona' e i rifiuti a comparire = fonti dichiarative negative</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Decima</t>
+          <t>Nona</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Serie di acquisizione e attribuzione delle chiavi (Voce 26 su 444 voci)</t>
+          <t>Fondo di 100 record di un servizio informativo estero (sala di lettura elettronica, marzo 2026)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Registro analitico integrale dei nodi (voce 47): chi attribuisce il dominio</t>
+          <t>Archivi del corpus: cia.gov/readingroom (ARCHIVI_OPERATIVO)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>L'attribuzione delle chiavi e' la classificazione per dominio del registro-nodi</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr"/>
+          <t>Distinzione indirizzo/atto: i 100 record sono 'indirizzi', non 'atti posseduti' - stessa cautela del corpus sugli URL non controllati</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Undicesima</t>
+          <t>Decima</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Un falsificatore messo alla prova; misura su 3 fascicoli (caso; disastro aereo; struttura clandestina)</t>
+          <t>Serie di acquisizione e attribuzione delle chiavi (Voce 26 su 444 voci)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Memoriale Moro e doppio fondo di via Montenevoso (voce 42); NASCO/Gladio (voci 41-42,44); Ustica</t>
+          <t>Registro analitico integrale dei nodi (voce 47): chi attribuisce il dominio</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>I tre fascicoli (Moro, Ustica, Gladio) sono tre grandi nodi del corpus; il 'falsificatore' rimanda alle manipolazioni del memoriale</t>
+          <t>L'attribuzione delle chiavi e' la classificazione per dominio del registro-nodi</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
@@ -857,25 +857,48 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>Undicesima</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Un falsificatore messo alla prova; misura su 3 fascicoli (caso; disastro aereo; struttura clandestina)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Memoriale Moro e doppio fondo di via Montenevoso (voce 42); NASCO/Gladio (voci 41-42,44); Ustica</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>I tre fascicoli (Moro, Ustica, Gladio) sono tre grandi nodi del corpus; il 'falsificatore' rimanda alle manipolazioni del memoriale</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>Dodicesima</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Lo strumento che esisteva: apparato dell'Indice generale atti X legislatura; autocorrezione del piu' grave dei 5 errori</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Statuto Savona come autocorrezione (l'opera si controlla anziche' farsi credere)</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>L'ente 'originatore' vs 'di provenienza' e' la distinzione produzione/acquisizione; l'autocorrezione e' il metodo del corpus</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1051,7 +1074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1109,22 +1132,34 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>PENDENZE dichiarate</t>
+          <t>Undicesima regola della risalita (app. settima)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Mancano dalla serie l'appendice PRIMA e l'appendice SETTIMA (non caricate): la Fase Settima non e' integra nel corpus. La 'quarta persona' (app. ottava) e il contenuto dell'audizione del ventuno gennaio duemila restano non posseduti (resoconto non disponibile). Le 19 unita' non individuate (app. quarta) restano aperte.</t>
+          <t>'Quando un organo dichiara il proprio standard, il grado delle sue ricostruzioni si fissa su quella dichiarazione e non sull'autorevolezza della sede. La sede conferisce pubblicita' e non conferisce grado.' Cio' consolida il fondamento della gradazione del corpus (Commissioni: A per le acquisizioni, B per le ricostruzioni): mutamento di natura, non di esito.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>PENDENZE dichiarate</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Con l'ingresso dell'appendice SETTIMA resta fuori dalla serie la sola appendice PRIMA (non caricata): il raccordo e' ora completo su undici appendici su dodici. La 'quarta persona' (app. ottava) e il contenuto dell'audizione del ventuno gennaio duemila restano non posseduti (resoconto non disponibile). Le 19 unita' non individuate (app. quarta) restano aperte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
           <t>Vincolo fonti</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Rispettato: nessuna interrogazione in rete per questo raccordo (lavoro sul solo corpus acquisito, come prescrive la Tavola Unica); nessun uso di Grokipedia ne' de il manifesto.</t>
         </is>

--- a/repertorio/ITALIA_NERA_RACCORDO_FASE_SETTIMA_MORO.xlsx
+++ b/repertorio/ITALIA_NERA_RACCORDO_FASE_SETTIMA_MORO.xlsx
@@ -610,7 +610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -650,22 +650,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Seconda</t>
+          <t>Prima (base)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Verifica genealogica: i tre atti; il collasso genealogico</t>
+          <t>Tavola accresciuta delle acquisizioni necessarie (accresce il Capitolo 69); 19 voci con condizione di chiusura e di smentita; REGOLA DI FERRO: 'dove la fonte documenta, l'opera certifica; dove la fonte tace, l'opera indaga e non afferma'</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Statuto Savona (tutte le voci 35-49); declassamento 'Skorpion via Dogali=arma di Moro' (voce 41)</t>
+          <t>Statuto Savona nella sua forma piu' pura (tutte le voci 35-52)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Il metodo della Fase Settima VALIDA il declassamento operato in voce 41: molte fonti collassano su poche perizie</t>
+          <t>La Regola di Ferro E' lo statuto del corpus, parola per parola: identita' fondativa fra le due linee</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr"/>
@@ -673,22 +673,22 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Terza</t>
+          <t>Seconda</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Primo repertorio di designazione per atto; il fascicolo MORO (X legislatura)</t>
+          <t>Verifica genealogica: i tre atti; il collasso genealogico</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Fonti della balistica Moro (voci 35-36) e commissioni Moro</t>
+          <t>Statuto Savona (tutte le voci 35-49); declassamento 'Skorpion via Dogali=arma di Moro' (voce 41)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>La designazione per atto e' il registro-nodi applicato agli atti parlamentari</t>
+          <t>Il metodo della Fase Settima VALIDA il declassamento operato in voce 41: molte fonti collassano su poche perizie</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
@@ -696,68 +696,68 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terza</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Chiusura dello Stato Zero sul fascicolo MORO; 19 unita' non individuate</t>
+          <t>Primo repertorio di designazione per atto; il fascicolo MORO (X legislatura)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Reperti irrisolti del caso Moro (PPK mai ritrovata, voce 39)</t>
+          <t>Fonti della balistica Moro (voci 35-36) e commissioni Moro</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Le 19 unita' non individuate sono l'omologo archivistico delle code irrisolte balistiche</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr"/>
+          <t>La designazione per atto e' il registro-nodi applicato agli atti parlamentari</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Catalogazione multipla e divergenza dei rinvii; collasso misurato</t>
+          <t>Chiusura dello Stato Zero sul fascicolo MORO; 19 unita' non individuate</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Trittico balistico (voci 37-39): convergenza di tipologia non identita'</t>
+          <t>Reperti irrisolti del caso Moro (PPK mai ritrovata, voce 39)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>La divergenza dei rinvii e' la stessa cautela della non-inferenza balistica</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr"/>
+          <t>Le 19 unita' non individuate sono l'omologo archivistico delle code irrisolte balistiche</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Sesta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Prima unita' di produzione: Relazione XI legislatura, doc. XXIII n.13</t>
+          <t>Catalogazione multipla e divergenza dei rinvii; collasso misurato</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Cronologia del caso Moro nel corpus</t>
+          <t>Trittico balistico (voci 37-39): convergenza di tipologia non identita'</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Fissa l'atto di produzione a monte delle esposizioni successive</t>
+          <t>La divergenza dei rinvii e' la stessa cautela della non-inferenza balistica</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr"/>
@@ -765,22 +765,22 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Settima</t>
+          <t>Sesta</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>L'organismo successore dichiara il proprio standard (XII leg., doc. XXIII n.1 e n.3, 1995): puo' andare 'oltre la prova processuale'. UNDICESIMA REGOLA: la sede conferisce pubblicita', non grado</t>
+          <t>Prima unita' di produzione: Relazione XI legislatura, doc. XXIII n.13</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Gradazione del corpus: atti delle Commissioni = A per le acquisizioni, B per le ricostruzioni/valutazioni</t>
+          <t>Cronologia del caso Moro nel corpus</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>FONDA la gradazione del corpus sulla dichiarazione della fonte medesima (non piu' solo prudenza dell'autore): es. Mastelloni/Hyperion doc. parlamentari registrati ma proscioglimento a C (voce 40)</t>
+          <t>Fissa l'atto di produzione a monte delle esposizioni successive</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr"/>
@@ -788,91 +788,91 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Ottava</t>
+          <t>Settima</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Canale orientale; quarta persona nella base; Stato Zero di quattro apparati (XIII leg., doc. XXIII n.37, sem. gen. 2000)</t>
+          <t>L'organismo successore dichiara il proprio standard (XII leg., doc. XXIII n.1 e n.3, 1995): puo' andare 'oltre la prova processuale'. UNDICESIMA REGOLA: la sede conferisce pubblicita', non grado</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>LODO MORO e canale OLP (voce 40); Hyperion/Superclan (voci 40,42)</t>
+          <t>Gradazione del corpus: atti delle Commissioni = A per le acquisizioni, B per le ricostruzioni/valutazioni</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Il 'canale orientale' della relazione parlamentare e' il quadro del lodo Moro/OLP gia' censito; la 'quarta persona' e i rifiuti a comparire = fonti dichiarative negative</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr"/>
+          <t>FONDA la gradazione del corpus sulla dichiarazione della fonte medesima (non piu' solo prudenza dell'autore): es. Mastelloni/Hyperion doc. parlamentari registrati ma proscioglimento a C (voce 40)</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Nona</t>
+          <t>Ottava</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Fondo di 100 record di un servizio informativo estero (sala di lettura elettronica, marzo 2026)</t>
+          <t>Canale orientale; quarta persona nella base; Stato Zero di quattro apparati (XIII leg., doc. XXIII n.37, sem. gen. 2000)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Archivi del corpus: cia.gov/readingroom (ARCHIVI_OPERATIVO)</t>
+          <t>LODO MORO e canale OLP (voce 40); Hyperion/Superclan (voci 40,42)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Distinzione indirizzo/atto: i 100 record sono 'indirizzi', non 'atti posseduti' - stessa cautela del corpus sugli URL non controllati</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr"/>
+          <t>Il 'canale orientale' della relazione parlamentare e' il quadro del lodo Moro/OLP gia' censito; la 'quarta persona' e i rifiuti a comparire = fonti dichiarative negative</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Decima</t>
+          <t>Nona</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Serie di acquisizione e attribuzione delle chiavi (Voce 26 su 444 voci)</t>
+          <t>Fondo di 100 record di un servizio informativo estero (sala di lettura elettronica, marzo 2026)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Registro analitico integrale dei nodi (voce 47): chi attribuisce il dominio</t>
+          <t>Archivi del corpus: cia.gov/readingroom (ARCHIVI_OPERATIVO)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>L'attribuzione delle chiavi e' la classificazione per dominio del registro-nodi</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr"/>
+          <t>Distinzione indirizzo/atto: i 100 record sono 'indirizzi', non 'atti posseduti' - stessa cautela del corpus sugli URL non controllati</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Undicesima</t>
+          <t>Decima</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Un falsificatore messo alla prova; misura su 3 fascicoli (caso; disastro aereo; struttura clandestina)</t>
+          <t>Serie di acquisizione e attribuzione delle chiavi (Voce 26 su 444 voci)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Memoriale Moro e doppio fondo di via Montenevoso (voce 42); NASCO/Gladio (voci 41-42,44); Ustica</t>
+          <t>Registro analitico integrale dei nodi (voce 47): chi attribuisce il dominio</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>I tre fascicoli (Moro, Ustica, Gladio) sono tre grandi nodi del corpus; il 'falsificatore' rimanda alle manipolazioni del memoriale</t>
+          <t>L'attribuzione delle chiavi e' la classificazione per dominio del registro-nodi</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
@@ -880,25 +880,94 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>Undicesima</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Un falsificatore messo alla prova; misura su 3 fascicoli (caso; disastro aereo; struttura clandestina)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Memoriale Moro e doppio fondo di via Montenevoso (voce 42); NASCO/Gladio (voci 41-42,44); Ustica</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>I tre fascicoli (Moro, Ustica, Gladio) sono tre grandi nodi del corpus; il 'falsificatore' rimanda alle manipolazioni del memoriale</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>Dodicesima</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Lo strumento che esisteva: apparato dell'Indice generale atti X legislatura; autocorrezione del piu' grave dei 5 errori</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Statuto Savona come autocorrezione (l'opera si controlla anziche' farsi credere)</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>L'ente 'originatore' vs 'di provenienza' e' la distinzione produzione/acquisizione; l'autocorrezione e' il metodo del corpus</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Quattordicesima</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>La classe di comparazione che non c'e': schede informative sulle STRAGI 1969-1984 (XI leg., 36 pagine); un errore respinto ('un errore che dispensa dal cercare')</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>NODI-STRAGI del corpus (voce 45): piazza Fontana, Bologna, piazza della Loggia, Peteano</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Aggancio diretto ai casi-strage gia' triangolati (voce 45); il rifiuto dell''errore che dispensa dal cercare' e' la non-inferenza del corpus</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Quindicesima</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>La relazione che non fu discussa: terza relazione semestrale XII leg., doc. XXIII n.7 (21.2.1996); una proposta depositata e non discussa</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Gradazione degli atti parlamentari (cfr. app. settima e voce 40)</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Una proposta depositata e non discussa non acquista grado dal deposito: corollario dell'undicesima regola (la sede non conferisce grado)</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1149,7 +1218,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Con l'ingresso dell'appendice SETTIMA resta fuori dalla serie la sola appendice PRIMA (non caricata): il raccordo e' ora completo su undici appendici su dodici. La 'quarta persona' (app. ottava) e il contenuto dell'audizione del ventuno gennaio duemila restano non posseduti (resoconto non disponibile). Le 19 unita' non individuate (app. quarta) restano aperte.</t>
+          <t>La serie si e' estesa alla QUINDICESIMA appendice; il corpus ne possiede ora QUATTORDICI (prima [base], seconda-dodicesima, quattordicesima, quindicesima). Resta fuori la sola appendice TREDICESIMA (non caricata). La 'quarta persona' (app. ottava) e il contenuto dell'audizione del ventuno gennaio duemila restano non posseduti; le 19 unita' non individuate (app. quarta) restano aperte.</t>
         </is>
       </c>
     </row>

--- a/repertorio/ITALIA_NERA_RACCORDO_FASE_SETTIMA_MORO.xlsx
+++ b/repertorio/ITALIA_NERA_RACCORDO_FASE_SETTIMA_MORO.xlsx
@@ -610,7 +610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -926,22 +926,22 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Quattordicesima</t>
+          <t>Tredicesima</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>La classe di comparazione che non c'e': schede informative sulle STRAGI 1969-1984 (XI leg., 36 pagine); un errore respinto ('un errore che dispensa dal cercare')</t>
+          <t>Una sola testimonianza formale (Voce 46): oggetto delle 27 sedute senza verbale posseduto; DIFETTO DELLA FONTE (l'OCR deforma gli ordinali: la prima seduta appare 18a) risolto per inferenza posizionale, verificata su 5 ancoraggi indipendenti; corregge la dodicesima</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>NODI-STRAGI del corpus (voce 45): piazza Fontana, Bologna, piazza della Loggia, Peteano</t>
+          <t>Statuto Savona: inferenza dichiarata come inferenza, falsificabile, verificata su ancoraggi; scarsita' di catene indipendenti</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Aggancio diretto ai casi-strage gia' triangolati (voce 45); il rifiuto dell''errore che dispensa dal cercare' e' la non-inferenza del corpus</t>
+          <t>Caso limpido della disciplina del corpus: 'una sola testimonianza formale' = conferma empirica del collasso genealogico (poche catene reali dietro molte fonti)</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr"/>
@@ -949,25 +949,48 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>Quattordicesima</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>La classe di comparazione che non c'e': schede informative sulle STRAGI 1969-1984 (XI leg., 36 pagine); un errore respinto ('un errore che dispensa dal cercare')</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>NODI-STRAGI del corpus (voce 45): piazza Fontana, Bologna, piazza della Loggia, Peteano</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Aggancio diretto ai casi-strage gia' triangolati (voce 45); il rifiuto dell''errore che dispensa dal cercare' e' la non-inferenza del corpus</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
           <t>Quindicesima</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>La relazione che non fu discussa: terza relazione semestrale XII leg., doc. XXIII n.7 (21.2.1996); una proposta depositata e non discussa</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Gradazione degli atti parlamentari (cfr. app. settima e voce 40)</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Una proposta depositata e non discussa non acquista grado dal deposito: corollario dell'undicesima regola (la sede non conferisce grado)</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1213,12 +1236,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>PENDENZE dichiarate</t>
+          <t>SERIE COMPLETA</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>La serie si e' estesa alla QUINDICESIMA appendice; il corpus ne possiede ora QUATTORDICI (prima [base], seconda-dodicesima, quattordicesima, quindicesima). Resta fuori la sola appendice TREDICESIMA (non caricata). La 'quarta persona' (app. ottava) e il contenuto dell'audizione del ventuno gennaio duemila restano non posseduti; le 19 unita' non individuate (app. quarta) restano aperte.</t>
+          <t>Con l'ingresso della TREDICESIMA il corpus possiede TUTTE le quindici appendici della Fase Settima (prima/base, seconda-quindicesima): il raccordo e' CHIUSO, nessuna appendice manca. Restano aperte, come pendenze interne alle appendici e non del raccordo, la 'quarta persona' (app. ottava), il contenuto dell'audizione del ventuno gennaio duemila, e le 19 unita' non individuate (app. quarta) - code documentali dichiarate, non colmate.</t>
         </is>
       </c>
     </row>
